--- a/data/trans_orig/IP07C02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C02-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62431</t>
+          <t>62977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81397</t>
+          <t>80318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39837</t>
+          <t>41085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>49819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65019</t>
+          <t>64491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63125</t>
+          <t>62187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100524</t>
+          <t>102649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122548</t>
+          <t>124268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45190</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59398</t>
+          <t>59119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80633</t>
+          <t>79932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56132</t>
+          <t>55530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>72511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55427</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>30224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44613</t>
+          <t>46265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>49450</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69984</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91002</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>39156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>62577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83845</t>
+          <t>83530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140579</t>
+          <t>140317</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167289</t>
+          <t>167296</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161542</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188731</t>
+          <t>188347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>309188</t>
+          <t>308857</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>349109</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105469</t>
+          <t>106491</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108056</t>
+          <t>107134</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>133371</t>
+          <t>135640</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220219</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259538</t>
+          <t>258693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>44599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64772</t>
+          <t>63724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>44248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63670</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83489</t>
+          <t>83881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>43208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>58399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81788</t>
+          <t>82147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104947</t>
+          <t>104281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>40926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56951</t>
+          <t>56465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46313</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76838</t>
+          <t>76757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98677</t>
+          <t>99233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32765</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,47 +5788,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>47,17%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>65,73%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>63352</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>55061</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>73036</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>47,43%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>63352</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>53612</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>71643</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>28791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>41737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51484</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69732</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>53480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>59806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81346</t>
+          <t>82246</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76838</t>
+          <t>75627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99257</t>
+          <t>98685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100975</t>
+          <t>102073</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>128628</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>152094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>260549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>304775</t>
+          <t>301516</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>154998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183507</t>
+          <t>183156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124779</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153081</t>
+          <t>153192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>287343</t>
+          <t>289336</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 95,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48359</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46971</t>
+          <t>47562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>71818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91821</t>
+          <t>91463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52024</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70171</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111387</t>
+          <t>112118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133865</t>
+          <t>134490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45776</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62343</t>
+          <t>61531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>83063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55496</t>
+          <t>55154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40284</t>
+          <t>40205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>88563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106334</t>
+          <t>106563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51040</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68891</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55780</t>
+          <t>56372</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72153</t>
+          <t>71629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112976</t>
+          <t>112267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136491</t>
+          <t>136555</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47214</t>
+          <t>48935</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>37215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80372</t>
+          <t>79952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,47 +10303,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7719</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8887</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198260</t>
+          <t>197602</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>225683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>199001</t>
+          <t>200208</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>229629</t>
+          <t>229570</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>405306</t>
+          <t>404043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>447615</t>
+          <t>447020</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,39%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>132564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>100066</t>
+          <t>100008</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>126966</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>252046</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33159</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
